--- a/output/pdf_financials_xlsx/IEI.xlsx
+++ b/output/pdf_financials_xlsx/IEI.xlsx
@@ -1131,49 +1131,49 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003242</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000125</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.003496</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>4.8e-05</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.031243</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.019636</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.044033</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.089834</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.048121</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.180589</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015038</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06768100000000001</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.187649</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.471818</v>
       </c>
     </row>
     <row r="13">
@@ -2159,49 +2159,49 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.76797</v>
+        <v>2.764728</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>10.367994</v>
+        <v>10.367869</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6.301691</v>
+        <v>6.298195</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.126125</v>
+        <v>9.126077</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>9.208653</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>5.811829</v>
+        <v>5.780586</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>6.409032</v>
+        <v>6.428668</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>3.864524</v>
+        <v>3.908557</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>5.87987</v>
+        <v>5.969704</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.41294</v>
+        <v>2.461061</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>8.526987999999999</v>
+        <v>8.707577000000001</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>9.804066000000001</v>
+        <v>9.819103999999999</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>8.567778000000001</v>
+        <v>8.635459000000001</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.607903</v>
+        <v>-2.420254</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>5.018352</v>
+        <v>5.49017</v>
       </c>
     </row>
     <row r="28">
@@ -2283,49 +2283,49 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.76797</v>
+        <v>2.764728</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>10.367994</v>
+        <v>10.367869</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.301691</v>
+        <v>6.298195</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.126125</v>
+        <v>9.126077</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>9.208653</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>5.811829</v>
+        <v>5.780586</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>6.409032</v>
+        <v>6.428668</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3.864524</v>
+        <v>3.908557</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>5.87987</v>
+        <v>5.969704</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.41294</v>
+        <v>2.461061</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>8.526987999999999</v>
+        <v>8.707577000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>9.804066000000001</v>
+        <v>9.819103999999999</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8.567778000000001</v>
+        <v>8.635459000000001</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.607903</v>
+        <v>-2.420254</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>5.018352</v>
+        <v>5.49017</v>
       </c>
     </row>
     <row r="30">
@@ -2630,13 +2630,13 @@
         <v>0.232998</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.424451</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.306017</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.27012</v>
       </c>
     </row>
     <row r="35">
@@ -2746,13 +2746,13 @@
         <v>0.232998</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.424451</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.306017</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.27012</v>
       </c>
     </row>
     <row r="37">
@@ -3442,13 +3442,13 @@
         <v>0.959742</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.917726</v>
+        <v>2.493275</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.91057</v>
+        <v>2.604553</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>6.824176</v>
+        <v>6.554056</v>
       </c>
     </row>
     <row r="49">
@@ -7898,16 +7898,16 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.155543</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.167449</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.199174</v>
       </c>
     </row>
     <row r="125">
@@ -7956,16 +7956,16 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.155543</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.167449</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.199174</v>
       </c>
     </row>
     <row r="126">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -29164,7 +29164,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -50665,7 +50669,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -57533,7 +57537,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -57636,7 +57640,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -58648,7 +58652,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -58749,7 +58753,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -62190,7 +62194,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -62289,7 +62293,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">

--- a/output/pdf_financials_xlsx/IEI.xlsx
+++ b/output/pdf_financials_xlsx/IEI.xlsx
@@ -44193,7 +44193,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -48187,7 +48191,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E408" s="5" t="n">
         <v>-0.0095</v>
       </c>

--- a/output/pdf_financials_xlsx/IEI.xlsx
+++ b/output/pdf_financials_xlsx/IEI.xlsx
@@ -656,15 +656,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -810,15 +806,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.030763</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.029894</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -872,15 +864,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -934,15 +922,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -996,15 +980,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.030763</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.029894</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1.266895</v>
@@ -1120,15 +1100,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.003242</v>
@@ -1182,15 +1158,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1244,15 +1216,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -1306,15 +1274,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -1368,15 +1332,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>0.54279</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.603784</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>2.76797</v>
@@ -1430,15 +1390,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0.181257</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0.307197</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0.563988</v>
@@ -1462,10 +1418,10 @@
         <v>1.671639</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-1.521911</v>
+        <v>1.521911</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.540616</v>
+        <v>-0.540616</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0.99705</v>
@@ -1676,15 +1632,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>0.361533</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0.296587</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>2.203982</v>
@@ -1738,15 +1690,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1761,10 +1709,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>0.019747</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>1.122963</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -1800,15 +1748,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -2148,15 +2092,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>0.54279</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0.603784</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>2.764728</v>
@@ -2210,15 +2150,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0.071767</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.070817</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -2272,15 +2208,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>0.614557</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0.674601</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>2.764728</v>
@@ -2426,15 +2358,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>33.39357762670646</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>50.87862546871067</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>20.37550985017901</v>
@@ -8605,7 +8533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U555"/>
+  <dimension ref="A1:U580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -26609,7 +26537,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -47197,7 +47129,11 @@
           <t>Future income tax</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E398" s="5" t="n">
         <v>0.040007</v>
       </c>
@@ -55270,7 +55206,11 @@
           <t>Income tax recovery (expense) 12(a)</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -59167,7 +59107,11 @@
           <t>Income from discontinued operations</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
@@ -59369,7 +59313,11 @@
           <t>Net income from discontinued operations</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E522" t="inlineStr">
         <is>
           <t>-</t>
@@ -62674,6 +62622,2501 @@
         </is>
       </c>
       <c r="U555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Rental revenue</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr"/>
+      <c r="E556" s="5" t="n">
+        <v>3.881647</v>
+      </c>
+      <c r="F556" s="5" t="n">
+        <v>3.867808</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Operating cost recoveries</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr"/>
+      <c r="E557" s="5" t="n">
+        <v>0.945774</v>
+      </c>
+      <c r="F557" s="5" t="n">
+        <v>1.001093</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Sales of pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr"/>
+      <c r="E558" s="5" t="n">
+        <v>12.853537</v>
+      </c>
+      <c r="F558" s="5" t="n">
+        <v>32.364447</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Other income                                                    17,299                                  ‐</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr"/>
+      <c r="E559" s="5" t="n">
+        <v>-0.009051</v>
+      </c>
+      <c r="F559" s="5" t="n">
+        <v>0.0009389999999999999</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Other income                                                    17,299                                  ‐</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Other income                                                    17,299                                  ‐ total</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr"/>
+      <c r="E560" s="5" t="n">
+        <v>17.671907</v>
+      </c>
+      <c r="F560" s="5" t="n">
+        <v>37.251586</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Property operations</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr"/>
+      <c r="E561" s="5" t="n">
+        <v>1.149422</v>
+      </c>
+      <c r="F561" s="5" t="n">
+        <v>1.07642</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Cost of sales of pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr"/>
+      <c r="E562" s="5" t="n">
+        <v>11.985822</v>
+      </c>
+      <c r="F562" s="5" t="n">
+        <v>30.771756</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Interest on mortgages, debentures and other financing</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr"/>
+      <c r="E563" s="5" t="n">
+        <v>1.274515</v>
+      </c>
+      <c r="F563" s="5" t="n">
+        <v>1.133438</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Amortization of revenue producing properties</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr"/>
+      <c r="E564" s="5" t="n">
+        <v>1.058146</v>
+      </c>
+      <c r="F564" s="5" t="n">
+        <v>0.988872</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Amortization of deferred leasing costs</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr"/>
+      <c r="E565" s="5" t="n">
+        <v>0.144636</v>
+      </c>
+      <c r="F565" s="5" t="n">
+        <v>0.131233</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Amortization of intangibles</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>AmortizationOfIntangibles</t>
+        </is>
+      </c>
+      <c r="E566" s="5" t="n">
+        <v>0.071767</v>
+      </c>
+      <c r="F566" s="5" t="n">
+        <v>0.070817</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Amortization of capital assets</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr"/>
+      <c r="E567" s="5" t="n">
+        <v>0.036944</v>
+      </c>
+      <c r="F567" s="5" t="n">
+        <v>0.042979</v>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Selling and administrative</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr"/>
+      <c r="E568" s="5" t="n">
+        <v>1.290416</v>
+      </c>
+      <c r="F568" s="5" t="n">
+        <v>1.762573</v>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Stock compensation                          15              540,190                                  ‐</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E569" s="5" t="n">
+        <v>0.086686</v>
+      </c>
+      <c r="F569" s="5" t="n">
+        <v>0.09963</v>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Stock compensation                          15              540,190                                  ‐</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Shareholder communications</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E570" s="5" t="n">
+        <v>0.030763</v>
+      </c>
+      <c r="F570" s="5" t="n">
+        <v>0.029894</v>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Stock compensation                          15              540,190                                  ‐</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Stock compensation                          15              540,190                                  ‐ total</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr"/>
+      <c r="E571" s="5" t="n">
+        <v>17.129117</v>
+      </c>
+      <c r="F571" s="5" t="n">
+        <v>36.647802</v>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Stock compensation                          15              540,190                                  ‐</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Earnings before income taxes</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E572" s="5" t="n">
+        <v>0.54279</v>
+      </c>
+      <c r="F572" s="5" t="n">
+        <v>0.603784</v>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Current income tax 13</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr"/>
+      <c r="E573" s="5" t="n">
+        <v>0.14125</v>
+      </c>
+      <c r="F573" s="5" t="n">
+        <v>0.137137</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Future income tax 13</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr"/>
+      <c r="E574" s="5" t="n">
+        <v>0.040007</v>
+      </c>
+      <c r="F574" s="5" t="n">
+        <v>0.17006</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Income taxes total</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr"/>
+      <c r="E575" s="5" t="n">
+        <v>0.181257</v>
+      </c>
+      <c r="F575" s="5" t="n">
+        <v>0.307197</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Net earnings and comprehensive income</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr"/>
+      <c r="E576" s="5" t="n">
+        <v>0.361533</v>
+      </c>
+      <c r="F576" s="5" t="n">
+        <v>0.296587</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Retained earnings, beginning of year</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr"/>
+      <c r="E577" s="5" t="n">
+        <v>4.301885</v>
+      </c>
+      <c r="F577" s="5" t="n">
+        <v>4.501395</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Net earnings</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E578" s="5" t="n">
+        <v>0.361533</v>
+      </c>
+      <c r="F578" s="5" t="n">
+        <v>0.296587</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Premium on shares cancelled 14</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr"/>
+      <c r="E579" s="5" t="n">
+        <v>-0.162023</v>
+      </c>
+      <c r="F579" s="5" t="n">
+        <v>-0.007993999999999999</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Retained earnings, end of year</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr"/>
+      <c r="E580" s="5" t="n">
+        <v>4.501395</v>
+      </c>
+      <c r="F580" s="5" t="n">
+        <v>4.789988</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
         <is>
           <t>-</t>
         </is>
